--- a/samples/03_monthly_consumption.xlsx
+++ b/samples/03_monthly_consumption.xlsx
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>140</v>
+        <v>350</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>90</v>
+        <v>220</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>

--- a/samples/03_monthly_consumption.xlsx
+++ b/samples/03_monthly_consumption.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,40 +424,45 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>tundish_type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>assignee_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>assignee_name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>material_name</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>month</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -471,38 +476,43 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>تاندیش اسلب</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>1001</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>علی رضایی</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>اسید سولفوریک</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>1404-06</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>350</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>لیتر</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>تأیید</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -512,38 +522,43 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>تاندیش بلوم</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>1001</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>علی رضایی</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>سود سوزآور</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>1404-06</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>220</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>کیلو</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -553,38 +568,43 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>تاندیش بلوم</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>1002</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>مریم احمدی</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>آب اکسیژنه</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>1404-06</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>500</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>لیتر</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>تأیید</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -594,38 +614,43 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>تاندیش اسلب</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>1003</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>حسین کریمی</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>کلر</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>1404-06</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>150</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>کیلو</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>تأیید</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -635,38 +660,43 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>تاندیش بیلت</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>1002</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>مریم احمدی</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>روغن صنعتی</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>1404-06</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>80</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>لیتر</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>بررسی</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
